--- a/ART MSF SUMMARY AS AT June 2025.xlsx
+++ b/ART MSF SUMMARY AS AT June 2025.xlsx
@@ -472,7 +472,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regina Caeli Hospital - Awka ART Monthly Summary Form As At June 2025</t>
+          <t>Iyi-Enu Hospital ART Monthly Summary Form As At June 2025</t>
         </is>
       </c>
     </row>
@@ -598,19 +598,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -622,7 +622,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R4" s="4" t="n"/>
     </row>
@@ -648,22 +648,22 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" s="4" t="n"/>
     </row>
@@ -950,52 +950,52 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="G12" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>503</v>
+        <v>425</v>
       </c>
       <c r="R12" s="4" t="n"/>
     </row>
@@ -1009,49 +1009,49 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="J13" t="n">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="K13" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="M13" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="n">
-        <v>912</v>
+        <v>763</v>
       </c>
     </row>
     <row r="14">
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R14" s="4" t="n"/>
     </row>
@@ -1162,7 +1162,7 @@
         <v/>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16"/>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>882</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20">
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F20" s="4" t="n"/>
     </row>
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>486</v>
+        <v>411</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>891</v>
+        <v>739</v>
       </c>
       <c r="F22" s="4" t="n"/>
     </row>
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>535</v>
+        <v>488</v>
       </c>
       <c r="F26" s="4" t="n"/>
     </row>
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="4" t="n"/>
     </row>
@@ -1379,16 +1379,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>343</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>481</v>
+        <v>410</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>880</v>
+        <v>731</v>
       </c>
       <c r="F30" s="4" t="n"/>
     </row>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>1415</v>
+        <v>1188</v>
       </c>
       <c r="C34" s="4" t="n"/>
     </row>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1569,37 +1569,37 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1627,16 +1627,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R40" s="4" t="n"/>
     </row>
@@ -1710,7 +1710,7 @@
         <v/>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1821,7 +1821,7 @@
         <v/>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1876,7 +1876,7 @@
         <v/>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R44" s="4" t="n"/>
     </row>
@@ -1985,49 +1985,49 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="E48" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>442</v>
+        <v>313</v>
       </c>
       <c r="R48" s="4" t="n"/>
     </row>
@@ -2041,49 +2041,49 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="I49" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="J49" t="n">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="K49" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="L49" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M49" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N49" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O49" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="P49" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="Q49" t="n">
-        <v>829</v>
+        <v>606</v>
       </c>
     </row>
     <row r="50">
@@ -2138,7 +2138,7 @@
         <v/>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R50" s="4" t="n"/>
     </row>
@@ -2194,7 +2194,7 @@
         <v/>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52"/>
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R56" s="4" t="n"/>
     </row>
@@ -2730,49 +2730,49 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="G64" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="L64" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="M64" s="4" t="n">
         <v>49</v>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v>47</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>414</v>
+        <v>293</v>
       </c>
       <c r="R64" s="4" t="n"/>
     </row>
@@ -2786,49 +2786,49 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F65" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H65" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="I65" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="K65" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="L65" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M65" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N65" t="n">
+        <v>44</v>
+      </c>
+      <c r="O65" t="n">
         <v>31</v>
       </c>
-      <c r="O65" t="n">
-        <v>24</v>
-      </c>
       <c r="P65" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="Q65" t="n">
-        <v>787</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66">
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R66" s="4" t="n"/>
     </row>
@@ -2939,7 +2939,7 @@
         <v/>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68"/>
@@ -3071,25 +3071,25 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>0</v>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="4" t="n"/>
     </row>
@@ -3478,46 +3478,46 @@
         <v>0</v>
       </c>
       <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4" t="n">
+      <c r="K80" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L80" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O80" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R80" s="4" t="n"/>
     </row>
@@ -3534,46 +3534,46 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" t="n">
         <v>2</v>
       </c>
-      <c r="H81" t="n">
+      <c r="K81" t="n">
         <v>4</v>
       </c>
-      <c r="I81" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" t="n">
-        <v>3</v>
-      </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
         <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82"/>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" s="4" t="n"/>
     </row>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>0</v>
@@ -3911,13 +3911,13 @@
         <v>0</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R90" s="4" t="n"/>
     </row>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92"/>
@@ -4093,49 +4093,49 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
         <v>3</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3</v>
-      </c>
-      <c r="E95" t="n">
-        <v>5</v>
       </c>
       <c r="F95" t="n">
         <v>3</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
+        <v>11</v>
+      </c>
+      <c r="I95" t="n">
+        <v>16</v>
+      </c>
+      <c r="J95" t="n">
+        <v>14</v>
+      </c>
+      <c r="K95" t="n">
         <v>13</v>
-      </c>
-      <c r="I95" t="n">
-        <v>22</v>
-      </c>
-      <c r="J95" t="n">
-        <v>24</v>
-      </c>
-      <c r="K95" t="n">
-        <v>22</v>
       </c>
       <c r="L95" t="n">
         <v>19</v>
       </c>
       <c r="M95" t="n">
+        <v>25</v>
+      </c>
+      <c r="N95" t="n">
         <v>16</v>
       </c>
-      <c r="N95" t="n">
-        <v>13</v>
-      </c>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q95" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96">
@@ -4148,49 +4148,49 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N96" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O96" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O96" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="P96" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="R96" s="4" t="n"/>
     </row>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>0</v>
@@ -4311,37 +4311,37 @@
         <v>0</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H100" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I100" s="4" t="n">
+      <c r="K100" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L100" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J100" s="4" t="n">
+      <c r="M100" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K100" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M100" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="N100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R100" s="4" t="n"/>
     </row>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4364,40 +4364,40 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>13</v>
+      </c>
+      <c r="J101" t="n">
         <v>8</v>
       </c>
-      <c r="H101" t="n">
-        <v>12</v>
-      </c>
-      <c r="I101" t="n">
-        <v>10</v>
-      </c>
-      <c r="J101" t="n">
+      <c r="K101" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" t="n">
         <v>4</v>
       </c>
-      <c r="K101" t="n">
-        <v>10</v>
-      </c>
-      <c r="L101" t="n">
-        <v>1</v>
-      </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102"/>
@@ -4505,49 +4505,49 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="n">
         <v>3</v>
       </c>
-      <c r="D105" t="n">
-        <v>3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>2</v>
       </c>
-      <c r="G105" t="n">
-        <v>5</v>
-      </c>
       <c r="H105" t="n">
+        <v>14</v>
+      </c>
+      <c r="I105" t="n">
+        <v>18</v>
+      </c>
+      <c r="J105" t="n">
+        <v>8</v>
+      </c>
+      <c r="K105" t="n">
+        <v>15</v>
+      </c>
+      <c r="L105" t="n">
         <v>12</v>
       </c>
-      <c r="I105" t="n">
-        <v>22</v>
-      </c>
-      <c r="J105" t="n">
-        <v>21</v>
-      </c>
-      <c r="K105" t="n">
-        <v>18</v>
-      </c>
-      <c r="L105" t="n">
-        <v>15</v>
-      </c>
       <c r="M105" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N105" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P105" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q105" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="106">
@@ -4560,49 +4560,49 @@
         <v>0</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G106" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="L106" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="H106" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="I106" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="J106" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="K106" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="L106" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="M106" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="Q106" s="4" t="n">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="R106" s="4" t="n"/>
     </row>
@@ -4726,34 +4726,34 @@
         <v>0</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R110" s="4" t="n"/>
     </row>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4776,31 +4776,31 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112"/>
@@ -4917,49 +4917,49 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>3</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5</v>
+      </c>
+      <c r="M115" t="n">
+        <v>4</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="D115" t="n">
+      <c r="P115" t="n">
         <v>2</v>
       </c>
-      <c r="E115" t="n">
-        <v>2</v>
-      </c>
-      <c r="F115" t="n">
-        <v>2</v>
-      </c>
-      <c r="G115" t="n">
-        <v>4</v>
-      </c>
-      <c r="H115" t="n">
-        <v>12</v>
-      </c>
-      <c r="I115" t="n">
-        <v>20</v>
-      </c>
-      <c r="J115" t="n">
-        <v>19</v>
-      </c>
-      <c r="K115" t="n">
-        <v>18</v>
-      </c>
-      <c r="L115" t="n">
-        <v>15</v>
-      </c>
-      <c r="M115" t="n">
-        <v>15</v>
-      </c>
-      <c r="N115" t="n">
-        <v>7</v>
-      </c>
-      <c r="O115" t="n">
-        <v>7</v>
-      </c>
-      <c r="P115" t="n">
-        <v>4</v>
-      </c>
       <c r="Q115" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116">
@@ -4972,49 +4972,49 @@
         <v>0</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D116" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E116" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K116" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F116" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H116" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I116" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K116" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="L116" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="M116" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="N116" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q116" s="4" t="n">
-        <v>265</v>
+        <v>59</v>
       </c>
       <c r="R116" s="4" t="n"/>
     </row>
